--- a/out/MLP-S4_repeat_2_000006.xlsx
+++ b/out/MLP-S4_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>3.248249220197788</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.248249220197788</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>3.248249220197788</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.248249220197788</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.648249220197788</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.248249220197788</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.248249220197788</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.248249220197788</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.248249220197788</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.248249220197788</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004499999204052146</v>
+        <v>-0.0003071606783388415</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5791847404061293</v>
+        <v>0.3953397196874989</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.248249220197788</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.159465998829599</v>
+        <v>0.7914276122940946</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.133757660132265</v>
+        <v>-0.09130019101537931</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.248249220197788</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3037323679937807</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.248249220197788</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3037323679937807</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>3.248249220197788</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4444370353973278</v>
+        <v>0.3034696345684717</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.659134738122588</v>
+        <v>0.8071737414596357</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.766010561876737</v>
+        <v>1.919424714250539</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.3174567996809165</v>
+        <v>0.1544436625708914</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.648249220197788</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.739367915652138</v>
+        <v>1.419960060811805</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.5560554741008308</v>
+        <v>0.2705225045981404</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.648249220197788</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.534178114534254</v>
+        <v>1.806637550012356</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.3045164510695438</v>
+        <v>0.1481479679930327</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>3.248249220197788</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.58667582090334</v>
+        <v>1.832177848859673</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.1257695322409667</v>
+        <v>0.06118746511389514</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.53337960014875</v>
+        <v>1.806249028819731</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1566980443581718</v>
+        <v>0.07623384035735191</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.648249220197788</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.721027854576633</v>
+        <v>1.89754049611885</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.09435305435328763</v>
+        <v>0.04590320979315803</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.752928602255588</v>
+        <v>1.913060361620847</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.07173368607520401</v>
+        <v>0.03489877952246592</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.648249220197788</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.802002601838335</v>
+        <v>1.936935095869529</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.03172799603222669</v>
+        <v>0.01543497241693593</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.793661640048533</v>
+        <v>1.93287712535679</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0251764037782078</v>
+        <v>0.01224790498878672</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.812275024873135</v>
+        <v>1.941931926081518</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01248238947441879</v>
+        <v>0.006071095559567959</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.648249220197788</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.812047135206845</v>
+        <v>1.941818482855961</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.007256365061091334</v>
+        <v>0.003526769705194263</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>3.248249220197788</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.814071288518452</v>
+        <v>1.942800628467314</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.003625682530545667</v>
+        <v>0.001760884852597131</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>3.248249220197788</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.814061768073611</v>
+        <v>1.942793429821467</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001788780453326182</v>
+        <v>0.0008688930413640376</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3648012947504815</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.814011325729142</v>
+        <v>1.942766308096926</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.001036347666705654</v>
+        <v>0.0005023232222412159</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.814294760568132</v>
+        <v>1.942901601796513</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0003431873377796176</v>
+        <v>0.000164629728661865</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.813942827975245</v>
+        <v>1.942728122666914</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001701717094871414</v>
+        <v>8.034006359629965e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.813939780126423</v>
+        <v>1.942724066973511</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.040164907423176e-05</v>
+        <v>4.147772647206162e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.813950511572034</v>
+        <v>1.942726633260618</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>4.240360893926523e-05</v>
+        <v>1.633162402266935e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.813942407800576</v>
+        <v>1.942720160456451</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>2.409200745629541e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.813948164937066</v>
+        <v>1.942720539024696</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>7.887479732251461e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.813939827785697</v>
+        <v>1.942713872060825</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.813936723100447</v>
+        <v>1.942710009985729</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.813932404109297</v>
+        <v>1.942705462673544</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.724541871943372e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.813927579936408</v>
+        <v>1.942705552618194</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.813926722002824</v>
+        <v>1.942704694684609</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.813926950323858</v>
+        <v>1.942704923005644</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.813926154659646</v>
+        <v>1.942704127341432</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.81392621692902</v>
+        <v>1.942704189610805</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.813926244604296</v>
+        <v>1.942704217286082</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.813926396818319</v>
+        <v>1.942704369500105</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.813926050877358</v>
+        <v>1.942704023559143</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.813926126984369</v>
+        <v>1.942704099666155</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.81392629303603</v>
+        <v>1.942704265717817</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.813926652814631</v>
+        <v>1.942704625496416</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.813926673571088</v>
+        <v>1.942704646252874</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.813926777353377</v>
+        <v>1.942704750035163</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.813927005674412</v>
+        <v>1.942704978356197</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.813926881135666</v>
+        <v>1.942704853817451</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.813926908810942</v>
+        <v>1.942704881492728</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.813926964161497</v>
+        <v>1.942704936843282</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.813927227076627</v>
+        <v>1.942705199758413</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.813927144050797</v>
+        <v>1.942705116732582</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.81392693648622</v>
+        <v>1.942704909168005</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.813926950323858</v>
+        <v>1.942704923005644</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.813927088700242</v>
+        <v>1.942705061382028</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.813926805028655</v>
+        <v>1.94270477771044</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.813926632058173</v>
+        <v>1.942704604739959</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.813926528275885</v>
+        <v>1.942704500957671</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.813926673571088</v>
+        <v>1.942704646252874</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.813926915729762</v>
+        <v>1.942704888411547</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.813926742759281</v>
+        <v>1.942704715441067</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.813926445250054</v>
+        <v>1.94270441793184</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.813926431412415</v>
+        <v>1.942704404094201</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.813926064714996</v>
+        <v>1.942704037396782</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.813926064714996</v>
+        <v>1.942704037396782</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.813926002445623</v>
+        <v>1.942703975127409</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.813925898663335</v>
+        <v>1.94270387134512</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.813925725692854</v>
+        <v>1.942703698374639</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.813925774124589</v>
+        <v>1.942703746806374</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.813925414345988</v>
+        <v>1.942703387027774</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.813925372833073</v>
+        <v>1.942703345514859</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.813925428183627</v>
+        <v>1.942703400865412</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.81392548353418</v>
+        <v>1.942703456215966</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.813925525047096</v>
+        <v>1.942703497728882</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.813925255213146</v>
+        <v>1.942703227894932</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.8139253105637</v>
+        <v>1.942703283245485</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.813925455858904</v>
+        <v>1.942703428540689</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.813925421264808</v>
+        <v>1.942703393946593</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.81392540742717</v>
+        <v>1.942703380108955</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.813925497371819</v>
+        <v>1.942703470053605</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>3.248249220197788</v>
+        <v>1.804705233669806</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.813925815637504</v>
+        <v>1.942703788319289</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.002580650042519</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.813925635748204</v>
+        <v>1.942703608429989</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.81392567726112</v>
+        <v>1.942703649942905</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.813925490453</v>
+        <v>1.942703463134786</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.813925559641193</v>
+        <v>1.942703532322978</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.813925358995435</v>
+        <v>1.94270333167722</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-1.602580650042519</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.81392540050835</v>
+        <v>1.942703373190136</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.204705233669806</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.813925428183627</v>
+        <v>1.942703400865412</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_2_000006.xlsx
+++ b/out/MLP-S4_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>3.248249220197788</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307028</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307029</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.648249220197788</v>
+        <v>0.3299763727307029</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.3299763727307028</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.3299763727307028</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.248249220197788</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004499999204052146</v>
+        <v>-0.0003504305209416197</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5791847404061293</v>
+        <v>0.4510313776757547</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.159465998829599</v>
+        <v>0.9029163236767631</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.133757660132265</v>
+        <v>-0.1041616839519103</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3465192632029026</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3465192632029026</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4444370353973278</v>
+        <v>0.346230759851238</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.659134738122588</v>
+        <v>0.8863445284685703</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.766010561876737</v>
+        <v>2.120685061092534</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.3174567996809165</v>
+        <v>0.1695920384993025</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.648249220197788</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.739367915652138</v>
+        <v>1.572230962598154</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.5560554741008308</v>
+        <v>0.2970567567531124</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.648249220197788</v>
+        <v>1.981656608135626</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.534178114534254</v>
+        <v>1.99683544618555</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.3045164510695438</v>
+        <v>0.1626790900703376</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>3.248249220197788</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.58667582090334</v>
+        <v>2.024880824597478</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.1257695322409667</v>
+        <v>0.06718863653004628</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.53337960014875</v>
+        <v>1.99640886318816</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1566980443581718</v>
+        <v>0.08371176579621106</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.648249220197788</v>
+        <v>0.3299763727307029</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.721027854576633</v>
+        <v>2.096654642005735</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.09435305435328763</v>
+        <v>0.05040470566371862</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9648012947504814</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.752928602255588</v>
+        <v>2.113696662953246</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.07173368607520401</v>
+        <v>0.03832202453146289</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.648249220197788</v>
+        <v>0.3299763727307029</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.802002601838335</v>
+        <v>2.139913286115416</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.03172799603222669</v>
+        <v>0.01694913678877288</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.329976372730703</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.793661640048533</v>
+        <v>2.135457325903188</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0251764037782078</v>
+        <v>0.01344847781189551</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.329976372730703</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.812275024873135</v>
+        <v>2.14540076448592</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01248238947441879</v>
+        <v>0.00666644786223456</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.648249220197788</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.812047135206845</v>
+        <v>2.145276674942901</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.007256365061091334</v>
+        <v>0.003875873794669808</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>3.248249220197788</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.814071288518452</v>
+        <v>2.146355948166096</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.003625682530545667</v>
+        <v>0.001935436897334904</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>3.248249220197788</v>
+        <v>1.355816490433165</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.814061768073611</v>
+        <v>2.146348532191169</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001788780453326182</v>
+        <v>0.0009522578380731069</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.814011325729142</v>
+        <v>2.146319265576441</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.001036347666705654</v>
+        <v>0.0005523880139097569</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.814294760568132</v>
+        <v>2.146468404049014</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0003431873377796176</v>
+        <v>0.0001802535194596684</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.813942827975245</v>
+        <v>2.14627830009377</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001701717094871414</v>
+        <v>8.932322818538381e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.813939780126423</v>
+        <v>2.14627434380106</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.040164907423176e-05</v>
+        <v>4.637011873227863e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.813950511572034</v>
+        <v>2.146277706539443</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>4.240360893926523e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.813942407800576</v>
+        <v>2.146271078546702</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>2.409200745629541e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.813948164937066</v>
+        <v>2.146271996782847</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>7.887479732251461e-06</v>
+        <v>2.732487839350877e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.813939827785697</v>
+        <v>2.146264994492026</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.813936723100447</v>
+        <v>2.14626113241693</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.813932404109297</v>
+        <v>2.146256585104745</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.724541871943372e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.813927579936408</v>
+        <v>2.146256675049395</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.813926722002824</v>
+        <v>2.14625581711581</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.813926950323858</v>
+        <v>2.146256045436845</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.813926154659646</v>
+        <v>2.146255249772633</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.81392621692902</v>
+        <v>2.146255312042006</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.813926244604296</v>
+        <v>2.146255339717283</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.813926396818319</v>
+        <v>2.146255491931306</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.813926050877358</v>
+        <v>2.146255145990344</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.813926126984369</v>
+        <v>2.146255222097356</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.81392629303603</v>
+        <v>2.146255388149017</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.813926652814631</v>
+        <v>2.146255747927617</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.813926673571088</v>
+        <v>2.146255768684075</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.813926777353377</v>
+        <v>2.146255872466364</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.813927005674412</v>
+        <v>2.146256100787399</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.813926881135666</v>
+        <v>2.146255976248652</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.813926908810942</v>
+        <v>2.146256003923929</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.813926964161497</v>
+        <v>2.146256059274483</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.813927227076627</v>
+        <v>2.146256322189614</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.813927144050797</v>
+        <v>2.146256239163783</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.81392693648622</v>
+        <v>2.146256031599206</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.813926950323858</v>
+        <v>2.146256045436845</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.813927088700242</v>
+        <v>2.146256183813229</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.813926805028655</v>
+        <v>2.14625590014164</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.813926632058173</v>
+        <v>2.14625572717116</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.813926528275885</v>
+        <v>2.146255623388872</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.813926673571088</v>
+        <v>2.146255768684075</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.813926915729762</v>
+        <v>2.146256010842749</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.813926742759281</v>
+        <v>2.146255837872268</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.813926445250054</v>
+        <v>2.146255540363041</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.813926431412415</v>
+        <v>2.146255526525402</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.813926064714996</v>
+        <v>2.146255159827982</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.813926064714996</v>
+        <v>2.146255159827982</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.813926002445623</v>
+        <v>2.14625509755861</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.813925898663335</v>
+        <v>2.146254993776321</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.813925725692854</v>
+        <v>2.14625482080584</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.813925774124589</v>
+        <v>2.146254869237575</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.813925414345988</v>
+        <v>2.146254509458975</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.813925372833073</v>
+        <v>2.14625446794606</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.813925428183627</v>
+        <v>2.146254523296613</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.81392548353418</v>
+        <v>2.146254578647167</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.813925525047096</v>
+        <v>2.146254620160083</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.813925255213146</v>
+        <v>2.146254350326132</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.8139253105637</v>
+        <v>2.146254405676686</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.813925455858904</v>
+        <v>2.14625455097189</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.813925421264808</v>
+        <v>2.146254516377794</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.81392540742717</v>
+        <v>2.146254502540156</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9648012947504814</v>
+        <v>0.529976372730703</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.813925497371819</v>
+        <v>2.146254592484806</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>3.248249220197788</v>
+        <v>0.529976372730703</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.813925815637504</v>
+        <v>2.14625491075049</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3648012947504815</v>
+        <v>0.5299763727307029</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.813925635748204</v>
+        <v>2.14625473086119</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3648012947504815</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.81392567726112</v>
+        <v>2.146254772374105</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.2958637449717587</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.813925490453</v>
+        <v>2.146254585565987</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.813925559641193</v>
+        <v>2.146254654754179</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.813925358995435</v>
+        <v>2.146254454108421</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.81392540050835</v>
+        <v>2.146254495621337</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9648012947504814</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.813925428183627</v>
+        <v>2.146254523296613</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_2_000006.xlsx
+++ b/out/MLP-S4_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4019736349582672</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4092080593109131</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4389511346817017</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4747504591941833</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4310254156589508</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.456379234790802</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4057630300521851</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4741029441356659</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4791836440563202</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.435088723897934</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4057040512561798</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3901613056659698</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4505467712879181</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4139170348644257</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4068126082420349</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4067327082157135</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4385536313056946</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4666686952114105</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.5100049376487732</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4571314454078674</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.436678946018219</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.2958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4075632691383362</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.2958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4224109351634979</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.494077742099762</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.43836909532547</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.3299763727307028</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5203621387481689</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.355816490433165</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.6410704255104065</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.181656608135626</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5506057739257812</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.355816490433165</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4851297736167908</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4926325380802155</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.2958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4355089664459229</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4178069829940796</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4389116764068604</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3299763727307029</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5583162307739258</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3299763727307029</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4971435964107513</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3299763727307028</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4805778861045837</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.3299763727307028</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5128456950187683</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4616286158561707</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4801615178585052</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5135659575462341</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.355816490433165</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5594170689582825</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.181656608135626</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5858893394470215</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.181656608135626</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6719293594360352</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.181656608135626</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003504305209416197</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4510313776757547</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6486839056015015</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.181656608135626</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9029163236767631</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1041616839519103</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5262090563774109</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.181656608135626</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3465192632029026</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.55611652135849</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.181656608135626</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3465192632029026</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5528738498687744</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.355816490433165</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.346230759851238</v>
+        <v>0.2123013248989449</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8863445284685703</v>
+        <v>0.2783048746353901</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4921561777591705</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.120685061092534</v>
+        <v>0.7694652442227462</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1695920384993025</v>
+        <v>0.05325043982180468</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.572166383266449</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.572230962598154</v>
+        <v>0.5972552420977619</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2970567567531124</v>
+        <v>0.09327319551786681</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5413229465484619</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.981656608135626</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.99683544618555</v>
+        <v>0.7305776076146511</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1626790900703376</v>
+        <v>0.05108003439471832</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.5477367639541626</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.16</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.024880824597478</v>
+        <v>0.739383649579078</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06718863653004628</v>
+        <v>0.0210966012868973</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4831450581550598</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.99640886318816</v>
+        <v>0.7304436639571162</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.08371176579621106</v>
+        <v>0.02628455481512958</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.6127570867538452</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.3299763727307029</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.096654642005735</v>
+        <v>0.7619203013701816</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.05040470566371862</v>
+        <v>0.01582669723685154</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4934356212615967</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.113696662953246</v>
+        <v>0.7672715049972902</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03832202453146289</v>
+        <v>0.01203227068582927</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.6797022819519043</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.3299763727307029</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.139913286115416</v>
+        <v>0.7755025763967033</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01694913678877288</v>
+        <v>0.005319128419633081</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3925088346004486</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.329976372730703</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.135457325903188</v>
+        <v>0.7741000719318202</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01344847781189551</v>
+        <v>0.004219704787200033</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.315613180398941</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.329976372730703</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.14540076448592</v>
+        <v>0.777218819608625</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.00666644786223456</v>
+        <v>0.002088738980386324</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.7803137302398682</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.155816490433164</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.145276674942901</v>
+        <v>0.7771764308077908</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003875873794669808</v>
+        <v>0.001213955112418778</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.7493639588356018</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.181656608135626</v>
+        <v>0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.146355948166096</v>
+        <v>0.7775119933868905</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001935436897334904</v>
+        <v>0.0006030229558365741</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5291834473609924</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.355816490433165</v>
+        <v>0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.146348532191169</v>
+        <v>0.7775062363572656</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009522578380731069</v>
+        <v>0.0002968380570500788</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4850247502326965</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5299763727307029</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.146319265576441</v>
+        <v>0.7774935956300393</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005523880139097569</v>
+        <v>0.0001685579444509423</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4995212256908417</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.146468404049014</v>
+        <v>0.7775370544039446</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001802535194596684</v>
+        <v>5.303122296326961e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3662067949771881</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.14627830009377</v>
+        <v>0.7774733097958993</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.932322818538381e-05</v>
+        <v>2.419528491452356e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3860926926136017</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.14627434380106</v>
+        <v>0.7774686466857942</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.637011873227863e-05</v>
+        <v>1.212337291075954e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.2995785176753998</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.146277706539443</v>
+        <v>0.777466434265255</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.3653273284435272</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.146271078546702</v>
+        <v>0.7774608925925246</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4068364202976227</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.146271996782847</v>
+        <v>0.7774580440198228</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3328972160816193</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.146264994492026</v>
+        <v>0.777452376589549</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3910408318042755</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.14626113241693</v>
+        <v>0.7774527571246067</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3313983380794525</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.146256585104745</v>
+        <v>0.7774529854456415</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3406074345111847</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.146256675049395</v>
+        <v>0.7774530753902914</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2791708409786224</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.14625581711581</v>
+        <v>0.7774522174567066</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3611766397953033</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.146256045436845</v>
+        <v>0.7774524457777413</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3197237849235535</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.146255249772633</v>
+        <v>0.7774516501135296</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.2524905502796173</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.146255312042006</v>
+        <v>0.7774517123829027</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.294335663318634</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.146255339717283</v>
+        <v>0.7774517400581795</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3375643193721771</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.146255491931306</v>
+        <v>0.7774518922722028</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3112712502479553</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.146255145990344</v>
+        <v>0.777451546331241</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3034289479255676</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.146255222097356</v>
+        <v>0.7774516224382527</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.2713664174079895</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.146255388149017</v>
+        <v>0.7774517884899143</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3703603744506836</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.146255747927617</v>
+        <v>0.7774521482685143</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4257211089134216</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.146255768684075</v>
+        <v>0.7774521690249721</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4300839304924011</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.146255872466364</v>
+        <v>0.7774522728072605</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.3635082840919495</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.146256100787399</v>
+        <v>0.7774525011282952</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3676437437534332</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.146255976248652</v>
+        <v>0.777452376589549</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3262860476970673</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.146256003923929</v>
+        <v>0.7774524042648259</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.3826662003993988</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.146256059274483</v>
+        <v>0.7774524596153798</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3363059461116791</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.146256322189614</v>
+        <v>0.7774527225305106</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.3596048653125763</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.146256239163783</v>
+        <v>0.7774526395046797</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3263881504535675</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.146256031599206</v>
+        <v>0.7774524319401029</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.3091751337051392</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.146256045436845</v>
+        <v>0.7774524457777413</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3373953998088837</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.146256183813229</v>
+        <v>0.777452584154126</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3294470012187958</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.14625590014164</v>
+        <v>0.7774523004825373</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2983077168464661</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.14625572717116</v>
+        <v>0.7774521275120566</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3673622012138367</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.146255623388872</v>
+        <v>0.7774520237297681</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3417814373970032</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.146255768684075</v>
+        <v>0.7774521690249721</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3319075107574463</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.146256010842749</v>
+        <v>0.7774524111836453</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3289402723312378</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.146255837872268</v>
+        <v>0.7774522382131642</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3155106604099274</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.146255540363041</v>
+        <v>0.7774519407039373</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3275634944438934</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.146255526525402</v>
+        <v>0.7774519268662988</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3310888409614563</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.146255159827982</v>
+        <v>0.7774515601688796</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3571438789367676</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.146255159827982</v>
+        <v>0.7774515601688796</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3829075396060944</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.14625509755861</v>
+        <v>0.7774514978995065</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3145551979541779</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.146254993776321</v>
+        <v>0.777451394117218</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3251971006393433</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.14625482080584</v>
+        <v>0.7774512211467373</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3616223335266113</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.146254869237575</v>
+        <v>0.7774512695784718</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3327732086181641</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.146254509458975</v>
+        <v>0.7774509097998717</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3229580521583557</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.14625446794606</v>
+        <v>0.7774508682869563</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.35490882396698</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.146254523296613</v>
+        <v>0.77745092363751</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3185250163078308</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.146254578647167</v>
+        <v>0.777450978988064</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.331886887550354</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.146254620160083</v>
+        <v>0.7774510205009794</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3355441689491272</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.146254350326132</v>
+        <v>0.7774507506670293</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3538582026958466</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.146254405676686</v>
+        <v>0.7774508060175832</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.356797993183136</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.14625455097189</v>
+        <v>0.7774509513127872</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3644295334815979</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.146254516377794</v>
+        <v>0.7774509167186909</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3425933718681335</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.146254502540156</v>
+        <v>0.7774509028810523</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4318422377109528</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.529976372730703</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.146254592484806</v>
+        <v>0.7774509928257025</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.5256434082984924</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.529976372730703</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.14625491075049</v>
+        <v>0.7774513110913872</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4192498624324799</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.5299763727307029</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.14625473086119</v>
+        <v>0.7774511312020871</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.400363028049469</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.2958637449717587</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.146254772374105</v>
+        <v>0.7774511727150024</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4076792001724243</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.2958637449717587</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.146254585565987</v>
+        <v>0.7774509859068831</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3680976927280426</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.146254654754179</v>
+        <v>0.7774510550950756</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3781543970108032</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.146254454108421</v>
+        <v>0.7774508544493178</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.345561295747757</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.5100000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.146254495621337</v>
+        <v>0.7774508959622332</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.3667456805706024</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.146254523296613</v>
+        <v>0.77745092363751</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_2_000006.xlsx
+++ b/out/MLP-S4_repeat_2_000006.xlsx
@@ -47849,7 +47849,7 @@
         <v>0.7803137302398682</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
         <v>0.7771764308077908</v>
@@ -48644,7 +48644,7 @@
         <v>0.7493639588356018</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC60" t="n">
         <v>0.7775119933868905</v>
@@ -49439,7 +49439,7 @@
         <v>0.5291834473609924</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
         <v>0.7775062363572656</v>
@@ -50234,7 +50234,7 @@
         <v>0.4850247502326965</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0.7774935956300393</v>
@@ -51029,7 +51029,7 @@
         <v>0.4995212256908417</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0.7775370544039446</v>
@@ -69314,7 +69314,7 @@
         <v>0.3676437437534332</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0.777452376589549</v>
@@ -70109,7 +70109,7 @@
         <v>0.3262860476970673</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0.7774524042648259</v>
@@ -70904,7 +70904,7 @@
         <v>0.3826662003993988</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0.7774524596153798</v>
@@ -71699,7 +71699,7 @@
         <v>0.3363059461116791</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0.7774527225305106</v>
@@ -72494,7 +72494,7 @@
         <v>0.3596048653125763</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0.7774526395046797</v>
@@ -76469,7 +76469,7 @@
         <v>0.2983077168464661</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5799999999999998</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC95" t="n">
         <v>0.7774521275120566</v>
